--- a/resources/templates/heyman/deregistration_contract.xlsx
+++ b/resources/templates/heyman/deregistration_contract.xlsx
@@ -443,7 +443,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">SELLER : SUNGSIN MOTORS CO.LTD</t>
+      <t xml:space="preserve">SELLER : HEYMAN LTD.</t>
     </r>
   </si>
   <si>
@@ -2580,7 +2580,7 @@
       <c r="C57" s="26" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">SELLER : SUNGSIN MOTORS CO.LTD</t>
+            <t xml:space="preserve">SELLER : HEYMAN LTD.</t>
           </r>
         </is>
       </c>

--- a/resources/templates/heyman/deregistration_contract.xlsx
+++ b/resources/templates/heyman/deregistration_contract.xlsx
@@ -38,7 +38,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">FAX : 82 - 031 - 499 - 1989</t>
+      <t xml:space="preserve">FAX : 82 - 505 - 366 - 9977</t>
     </r>
   </si>
   <si>
@@ -1310,7 +1310,7 @@
       <c r="E5" s="5" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">FAX : 82 - 031 - 499 - 1989</t>
+            <t xml:space="preserve">FAX : 82 - 505 - 366 - 9977</t>
           </r>
         </is>
       </c>

--- a/resources/templates/heyman/deregistration_contract.xlsx
+++ b/resources/templates/heyman/deregistration_contract.xlsx
@@ -23,22 +23,22 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">export 2 area 194-75 Okryendong Yeonsugu incheon  Korea  </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">63 sunghyeonro ilsandonggu Kyeonggydo  Korea</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">TEL : 82 -10-9009-9977</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">FAX : 82 - 505 - 366 - 9977</t>
+      <t xml:space="preserve">#513, THE PARK 365, 50 Seonyudong1-ro,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Yeongdeungpo-gu, Seoul, Korea</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">TEL : 82-10-9009-9977</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">FAX : 82-505-366-9977</t>
     </r>
   </si>
   <si>
@@ -1275,7 +1275,7 @@
       <c r="A2" s="33" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">export 2 area 194-75 Okryendong Yeonsugu incheon  Korea  </t>
+            <t xml:space="preserve">#513, THE PARK 365, 50 Seonyudong1-ro,</t>
           </r>
         </is>
       </c>
@@ -1284,7 +1284,7 @@
       <c r="A3" s="33" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">63 sunghyeonro ilsandonggu Kyeonggydo  Korea</t>
+            <t xml:space="preserve">Yeongdeungpo-gu, Seoul, Korea</t>
           </r>
         </is>
       </c>
@@ -1297,7 +1297,7 @@
       <c r="E4" s="5" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">TEL : 82 -10-9009-9977</t>
+            <t xml:space="preserve">TEL : 82-10-9009-9977</t>
           </r>
         </is>
       </c>
@@ -1310,7 +1310,7 @@
       <c r="E5" s="5" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">FAX : 82 - 505 - 366 - 9977</t>
+            <t xml:space="preserve">FAX : 82-505-366-9977</t>
           </r>
         </is>
       </c>
